--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>891.5119999999999</v>
+        <v>877.552</v>
       </c>
       <c r="D2">
-        <v>58.285</v>
+        <v>55.244</v>
       </c>
       <c r="E2">
-        <v>7.634</v>
+        <v>7.433</v>
       </c>
       <c r="F2">
-        <v>0.241</v>
+        <v>0.235</v>
       </c>
       <c r="G2">
-        <v>876.223</v>
+        <v>862.651</v>
       </c>
       <c r="H2">
-        <v>906.149</v>
+        <v>891.7859999999999</v>
       </c>
       <c r="I2">
-        <v>876.4880000000001</v>
+        <v>862.8920000000001</v>
       </c>
       <c r="J2">
-        <v>906.077</v>
+        <v>891.436</v>
       </c>
       <c r="K2">
-        <v>876.62</v>
+        <v>863.335</v>
       </c>
       <c r="L2">
-        <v>906.21</v>
+        <v>891.879</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>414.555</v>
+        <v>248.158</v>
       </c>
       <c r="D3">
-        <v>49.669</v>
+        <v>19.371</v>
       </c>
       <c r="E3">
-        <v>7.048</v>
+        <v>4.401</v>
       </c>
       <c r="F3">
-        <v>0.223</v>
+        <v>0.139</v>
       </c>
       <c r="G3">
-        <v>400.555</v>
+        <v>239.305</v>
       </c>
       <c r="H3">
-        <v>428.182</v>
+        <v>256.558</v>
       </c>
       <c r="I3">
-        <v>401.543</v>
+        <v>239.56</v>
       </c>
       <c r="J3">
-        <v>428.826</v>
+        <v>257.096</v>
       </c>
       <c r="K3">
-        <v>400.098</v>
+        <v>238.993</v>
       </c>
       <c r="L3">
-        <v>427.381</v>
+        <v>256.53</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>995.044</v>
+        <v>979.496</v>
       </c>
       <c r="D4">
-        <v>74.621</v>
+        <v>70.373</v>
       </c>
       <c r="E4">
-        <v>8.638</v>
+        <v>8.388999999999999</v>
       </c>
       <c r="F4">
-        <v>0.273</v>
+        <v>0.265</v>
       </c>
       <c r="G4">
-        <v>978.264</v>
+        <v>963.122</v>
       </c>
       <c r="H4">
-        <v>1012.126</v>
+        <v>996.005</v>
       </c>
       <c r="I4">
-        <v>977.573</v>
+        <v>962.1609999999999</v>
       </c>
       <c r="J4">
-        <v>1011.029</v>
+        <v>994.966</v>
       </c>
       <c r="K4">
-        <v>979.21</v>
+        <v>964.0940000000001</v>
       </c>
       <c r="L4">
-        <v>1012.666</v>
+        <v>996.899</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>443.688</v>
+        <v>277.013</v>
       </c>
       <c r="D5">
-        <v>55.031</v>
+        <v>23.466</v>
       </c>
       <c r="E5">
-        <v>7.418</v>
+        <v>4.844</v>
       </c>
       <c r="F5">
-        <v>0.235</v>
+        <v>0.153</v>
       </c>
       <c r="G5">
-        <v>428.98</v>
+        <v>267.337</v>
       </c>
       <c r="H5">
-        <v>458.059</v>
+        <v>286.326</v>
       </c>
       <c r="I5">
-        <v>428.943</v>
+        <v>266.449</v>
       </c>
       <c r="J5">
-        <v>457.904</v>
+        <v>286.335</v>
       </c>
       <c r="K5">
-        <v>429.303</v>
+        <v>267.509</v>
       </c>
       <c r="L5">
-        <v>458.264</v>
+        <v>287.395</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>877.552</v>
+        <v>902.7089999999999</v>
       </c>
       <c r="D2">
-        <v>55.244</v>
+        <v>59.804</v>
       </c>
       <c r="E2">
-        <v>7.433</v>
+        <v>7.733</v>
       </c>
       <c r="F2">
-        <v>0.235</v>
+        <v>0.245</v>
       </c>
       <c r="G2">
-        <v>862.651</v>
+        <v>887.231</v>
       </c>
       <c r="H2">
-        <v>891.7859999999999</v>
+        <v>917.545</v>
       </c>
       <c r="I2">
-        <v>862.8920000000001</v>
+        <v>887.482</v>
       </c>
       <c r="J2">
-        <v>891.436</v>
+        <v>917.396</v>
       </c>
       <c r="K2">
-        <v>863.335</v>
+        <v>887.701</v>
       </c>
       <c r="L2">
-        <v>891.879</v>
+        <v>917.614</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>248.158</v>
+        <v>256.696</v>
       </c>
       <c r="D3">
-        <v>19.371</v>
+        <v>20.515</v>
       </c>
       <c r="E3">
-        <v>4.401</v>
+        <v>4.529</v>
       </c>
       <c r="F3">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="G3">
-        <v>239.305</v>
+        <v>247.597</v>
       </c>
       <c r="H3">
-        <v>256.558</v>
+        <v>265.351</v>
       </c>
       <c r="I3">
-        <v>239.56</v>
+        <v>248.06</v>
       </c>
       <c r="J3">
-        <v>257.096</v>
+        <v>265.841</v>
       </c>
       <c r="K3">
-        <v>238.993</v>
+        <v>247.328</v>
       </c>
       <c r="L3">
-        <v>256.53</v>
+        <v>265.11</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>979.496</v>
+        <v>1007.575</v>
       </c>
       <c r="D4">
-        <v>70.373</v>
+        <v>76.548</v>
       </c>
       <c r="E4">
-        <v>8.388999999999999</v>
+        <v>8.749000000000001</v>
       </c>
       <c r="F4">
-        <v>0.265</v>
+        <v>0.277</v>
       </c>
       <c r="G4">
-        <v>963.122</v>
+        <v>990.522</v>
       </c>
       <c r="H4">
-        <v>996.005</v>
+        <v>1024.818</v>
       </c>
       <c r="I4">
-        <v>962.1609999999999</v>
+        <v>989.472</v>
       </c>
       <c r="J4">
-        <v>994.966</v>
+        <v>1023.705</v>
       </c>
       <c r="K4">
-        <v>964.0940000000001</v>
+        <v>991.54</v>
       </c>
       <c r="L4">
-        <v>996.899</v>
+        <v>1025.773</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>277.013</v>
+        <v>286.545</v>
       </c>
       <c r="D5">
-        <v>23.466</v>
+        <v>24.862</v>
       </c>
       <c r="E5">
-        <v>4.844</v>
+        <v>4.986</v>
       </c>
       <c r="F5">
-        <v>0.153</v>
+        <v>0.158</v>
       </c>
       <c r="G5">
-        <v>267.337</v>
+        <v>276.595</v>
       </c>
       <c r="H5">
-        <v>286.326</v>
+        <v>296.14</v>
       </c>
       <c r="I5">
-        <v>266.449</v>
+        <v>275.774</v>
       </c>
       <c r="J5">
-        <v>286.335</v>
+        <v>296.172</v>
       </c>
       <c r="K5">
-        <v>267.509</v>
+        <v>276.741</v>
       </c>
       <c r="L5">
-        <v>287.395</v>
+        <v>297.139</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>902.7089999999999</v>
+        <v>898.373</v>
       </c>
       <c r="D2">
-        <v>59.804</v>
+        <v>56.646</v>
       </c>
       <c r="E2">
-        <v>7.733</v>
+        <v>7.526</v>
       </c>
       <c r="F2">
-        <v>0.245</v>
+        <v>0.238</v>
       </c>
       <c r="G2">
-        <v>887.231</v>
+        <v>883.331</v>
       </c>
       <c r="H2">
-        <v>917.545</v>
+        <v>912.8339999999999</v>
       </c>
       <c r="I2">
-        <v>887.482</v>
+        <v>883.8819999999999</v>
       </c>
       <c r="J2">
-        <v>917.396</v>
+        <v>913.042</v>
       </c>
       <c r="K2">
-        <v>887.701</v>
+        <v>883.414</v>
       </c>
       <c r="L2">
-        <v>917.614</v>
+        <v>912.574</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>256.696</v>
+        <v>252.756</v>
       </c>
       <c r="D3">
-        <v>20.515</v>
+        <v>19.373</v>
       </c>
       <c r="E3">
-        <v>4.529</v>
+        <v>4.401</v>
       </c>
       <c r="F3">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="G3">
-        <v>247.597</v>
+        <v>243.898</v>
       </c>
       <c r="H3">
-        <v>265.351</v>
+        <v>261.152</v>
       </c>
       <c r="I3">
-        <v>248.06</v>
+        <v>244.02</v>
       </c>
       <c r="J3">
-        <v>265.841</v>
+        <v>261.882</v>
       </c>
       <c r="K3">
-        <v>247.328</v>
+        <v>243.399</v>
       </c>
       <c r="L3">
-        <v>265.11</v>
+        <v>261.261</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1007.575</v>
+        <v>1002.731</v>
       </c>
       <c r="D4">
-        <v>76.548</v>
+        <v>73.702</v>
       </c>
       <c r="E4">
-        <v>8.749000000000001</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="F4">
-        <v>0.277</v>
+        <v>0.271</v>
       </c>
       <c r="G4">
-        <v>990.522</v>
+        <v>986.042</v>
       </c>
       <c r="H4">
-        <v>1024.818</v>
+        <v>1019.694</v>
       </c>
       <c r="I4">
-        <v>989.472</v>
+        <v>984.595</v>
       </c>
       <c r="J4">
-        <v>1023.705</v>
+        <v>1018.956</v>
       </c>
       <c r="K4">
-        <v>991.54</v>
+        <v>986.643</v>
       </c>
       <c r="L4">
-        <v>1025.773</v>
+        <v>1021.004</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>286.545</v>
+        <v>282.11</v>
       </c>
       <c r="D5">
-        <v>24.862</v>
+        <v>23.473</v>
       </c>
       <c r="E5">
-        <v>4.986</v>
+        <v>4.845</v>
       </c>
       <c r="F5">
-        <v>0.158</v>
+        <v>0.153</v>
       </c>
       <c r="G5">
-        <v>276.595</v>
+        <v>272.499</v>
       </c>
       <c r="H5">
-        <v>296.14</v>
+        <v>291.491</v>
       </c>
       <c r="I5">
-        <v>275.774</v>
+        <v>272.236</v>
       </c>
       <c r="J5">
-        <v>296.172</v>
+        <v>291.565</v>
       </c>
       <c r="K5">
-        <v>276.741</v>
+        <v>272.541</v>
       </c>
       <c r="L5">
-        <v>297.139</v>
+        <v>291.87</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>898.373</v>
+        <v>919.567</v>
       </c>
       <c r="D2">
-        <v>56.646</v>
+        <v>64.244</v>
       </c>
       <c r="E2">
-        <v>7.526</v>
+        <v>8.015000000000001</v>
       </c>
       <c r="F2">
-        <v>0.238</v>
+        <v>0.253</v>
       </c>
       <c r="G2">
-        <v>883.331</v>
+        <v>903.578</v>
       </c>
       <c r="H2">
-        <v>912.8339999999999</v>
+        <v>934.997</v>
       </c>
       <c r="I2">
-        <v>883.8819999999999</v>
+        <v>903.303</v>
       </c>
       <c r="J2">
-        <v>913.042</v>
+        <v>934.951</v>
       </c>
       <c r="K2">
-        <v>883.414</v>
+        <v>903.904</v>
       </c>
       <c r="L2">
-        <v>912.574</v>
+        <v>935.551</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>252.756</v>
+        <v>264.63</v>
       </c>
       <c r="D3">
-        <v>19.373</v>
+        <v>22.556</v>
       </c>
       <c r="E3">
-        <v>4.401</v>
+        <v>4.749</v>
       </c>
       <c r="F3">
-        <v>0.139</v>
+        <v>0.15</v>
       </c>
       <c r="G3">
-        <v>243.898</v>
+        <v>255.139</v>
       </c>
       <c r="H3">
-        <v>261.152</v>
+        <v>273.756</v>
       </c>
       <c r="I3">
-        <v>244.02</v>
+        <v>255.346</v>
       </c>
       <c r="J3">
-        <v>261.882</v>
+        <v>274.244</v>
       </c>
       <c r="K3">
-        <v>243.399</v>
+        <v>254.834</v>
       </c>
       <c r="L3">
-        <v>261.261</v>
+        <v>273.731</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1002.731</v>
+        <v>1026.43</v>
       </c>
       <c r="D4">
-        <v>73.702</v>
+        <v>82.569</v>
       </c>
       <c r="E4">
-        <v>8.585000000000001</v>
+        <v>9.087</v>
       </c>
       <c r="F4">
-        <v>0.271</v>
+        <v>0.287</v>
       </c>
       <c r="G4">
-        <v>986.042</v>
+        <v>1008.694</v>
       </c>
       <c r="H4">
-        <v>1019.694</v>
+        <v>1044.313</v>
       </c>
       <c r="I4">
-        <v>984.595</v>
+        <v>1007.524</v>
       </c>
       <c r="J4">
-        <v>1018.956</v>
+        <v>1043.919</v>
       </c>
       <c r="K4">
-        <v>986.643</v>
+        <v>1009.015</v>
       </c>
       <c r="L4">
-        <v>1021.004</v>
+        <v>1045.41</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>282.11</v>
+        <v>295.414</v>
       </c>
       <c r="D5">
-        <v>23.473</v>
+        <v>27.538</v>
       </c>
       <c r="E5">
-        <v>4.845</v>
+        <v>5.248</v>
       </c>
       <c r="F5">
-        <v>0.153</v>
+        <v>0.166</v>
       </c>
       <c r="G5">
-        <v>272.499</v>
+        <v>284.973</v>
       </c>
       <c r="H5">
-        <v>291.491</v>
+        <v>305.544</v>
       </c>
       <c r="I5">
-        <v>272.236</v>
+        <v>284.229</v>
       </c>
       <c r="J5">
-        <v>291.565</v>
+        <v>305.537</v>
       </c>
       <c r="K5">
-        <v>272.541</v>
+        <v>285.136</v>
       </c>
       <c r="L5">
-        <v>291.87</v>
+        <v>306.444</v>
       </c>
     </row>
   </sheetData>
